--- a/data/human_calibration/human_calibration_labeling_RU_reference.xlsx
+++ b/data/human_calibration/human_calibration_labeling_RU_reference.xlsx
@@ -28,15 +28,18 @@
     <font>
       <name val="Arial"/>
       <i val="1"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
     </font>
   </fonts>
